--- a/OUTPUT/direct_A0A0B6P4W3_Yersinia_pestis_KIM10_.xlsx
+++ b/OUTPUT/direct_A0A0B6P4W3_Yersinia_pestis_KIM10_.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0086</v>
+        <v>0.008796481407437025</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.2724</v>
+        <v>0.2724910035985606</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.2172</v>
+        <v>0.217313074770092</v>
       </c>
     </row>
   </sheetData>
